--- a/Result/profitability/4974.xlsx
+++ b/Result/profitability/4974.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>1.34125</v>
+        <v>1.27875</v>
       </c>
       <c r="N2" t="n">
-        <v>14.66</v>
+        <v>14.40375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>1.26375</v>
+        <v>1.2</v>
       </c>
       <c r="N3" t="n">
-        <v>13.64</v>
+        <v>13.64875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.84</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.0775</v>
       </c>
       <c r="N4" t="n">
-        <v>13.08625</v>
+        <v>12.81375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9875</v>
+        <v>1.04375</v>
       </c>
       <c r="N5" t="n">
-        <v>12.00625</v>
+        <v>11.72</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.21</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02</v>
+        <v>1.01875</v>
       </c>
       <c r="N6" t="n">
-        <v>11.325</v>
+        <v>11.2925</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.905</v>
+        <v>0.9575</v>
       </c>
       <c r="N7" t="n">
-        <v>10.49125</v>
+        <v>10.72625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4974</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D69" t="n">
+        <v>901</v>
+      </c>
+      <c r="E69" t="n">
+        <v>158</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="G69" t="n">
+        <v>109</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>10.29%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>14</v>
+      </c>
+      <c r="J69" t="n">
+        <v>123</v>
+      </c>
+      <c r="K69" t="n">
+        <v>102</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.4325</v>
+      </c>
+      <c r="N69" t="n">
+        <v>15.2675</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.3099999999999998</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0.2844036697247705</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.1383792048929664</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.4736842105263157</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-2.289999999999999</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.1332945285215367</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
